--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.1436</v>
+        <v>16.92546</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5424</v>
+        <v>16.78625</v>
       </c>
       <c r="E2" t="n">
-        <v>17.05511</v>
+        <v>16.87433</v>
       </c>
       <c r="F2" t="n">
-        <v>43.39201</v>
+        <v>42.71157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05292</v>
+        <v>0.05153</v>
       </c>
       <c r="H2" t="n">
-        <v>1.88783</v>
+        <v>1.87814</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.27395</v>
+        <v>17.01781</v>
       </c>
       <c r="D3" t="n">
-        <v>17.09173</v>
+        <v>16.7967</v>
       </c>
       <c r="E3" t="n">
-        <v>17.15396</v>
+        <v>16.89337</v>
       </c>
       <c r="F3" t="n">
-        <v>43.80065</v>
+        <v>43.34116</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05144</v>
+        <v>0.05122</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82588</v>
+        <v>1.86647</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.25474</v>
+        <v>17.15982</v>
       </c>
       <c r="D4" t="n">
-        <v>17.13328</v>
+        <v>16.94467</v>
       </c>
       <c r="E4" t="n">
-        <v>17.23361</v>
+        <v>17.1531</v>
       </c>
       <c r="F4" t="n">
-        <v>42.97319</v>
+        <v>42.84249</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05162</v>
+        <v>0.05184</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85183</v>
+        <v>1.8931</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.86351</v>
+        <v>17.52929</v>
       </c>
       <c r="D6" t="n">
-        <v>16.19544</v>
+        <v>16.27682</v>
       </c>
       <c r="E6" t="n">
-        <v>16.85727</v>
+        <v>16.75967</v>
       </c>
       <c r="F6" t="n">
-        <v>21.78724</v>
+        <v>22.18405</v>
       </c>
       <c r="G6" t="n">
-        <v>34.80348</v>
+        <v>34.48701</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.01965</v>
+        <v>17.06235</v>
       </c>
       <c r="D7" t="n">
-        <v>15.96835</v>
+        <v>16.32004</v>
       </c>
       <c r="E7" t="n">
-        <v>16.71614</v>
+        <v>16.90453</v>
       </c>
       <c r="F7" t="n">
-        <v>22.1692</v>
+        <v>22.51001</v>
       </c>
       <c r="G7" t="n">
-        <v>35.02254</v>
+        <v>33.75704</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.7965</v>
+        <v>17.18323</v>
       </c>
       <c r="D8" t="n">
-        <v>15.96849</v>
+        <v>16.1109</v>
       </c>
       <c r="E8" t="n">
-        <v>16.74793</v>
+        <v>16.64877</v>
       </c>
       <c r="F8" t="n">
-        <v>22.44527</v>
+        <v>22.20831</v>
       </c>
       <c r="G8" t="n">
-        <v>34.99623</v>
+        <v>34.41999</v>
       </c>
     </row>
   </sheetData>
